--- a/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment Theses" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Quality" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stop-Loss Backtests" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,7 +525,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-04 18:47 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-04 18:50 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4790,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:47:49.055074+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:50:25.797519+00:00'}</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4812,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:47:49.057353+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:50:25.800034+00:00'}</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4834,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2021-07-28', 'rows': 1302, 'fetched_utc': '2026-10-04T18:47:49.059485+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2021-07-28', 'rows': 1302, 'fetched_utc': '2026-10-04T18:50:25.801697+00:00'}</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4856,7 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:47:49.061306+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:50:25.803463+00:00'}</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4878,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:47:49.062973+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:50:25.805187+00:00'}</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4900,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2010-09-09', 'rows': 4041, 'fetched_utc': '2026-10-04T18:47:49.064882+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2010-09-09', 'rows': 4041, 'fetched_utc': '2026-10-04T18:50:25.806728+00:00'}</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4922,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:47:49.067067+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:50:25.808489+00:00'}</t>
         </is>
       </c>
     </row>
@@ -4943,7 +4944,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2003-09-29', 'rows': 5790, 'fetched_utc': '2026-10-04T18:47:49.068793+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2003-09-29', 'rows': 5790, 'fetched_utc': '2026-10-04T18:50:25.810154+00:00'}</t>
         </is>
       </c>
     </row>
@@ -5590,6 +5591,2516 @@
       <c r="F27" s="10" t="inlineStr">
         <is>
           <t>P1 Critical</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Stop-Loss Backtests (historical, not advice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>cagr</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>vol</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>sharpe</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>sortino</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>max_drawdown</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>total_return</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>turnover</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>missed_upside</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>reentry_days</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>0.1056477327058141</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>0.4213253873361095</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0.4500467123039825</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>0.5948922664284093</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>-0.7988731794932153</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>13.60490660949948</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0.04333410037786645</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0.3808985868135027</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.3024574566004236</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0.3927817450261595</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>-0.8433772282571956</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>2.103147965050269</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>1.987099071931526</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0.07507433755581072</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0.4060459850090875</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.3827143334361712</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0.496826617070116</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>-0.7434811353827333</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>5.906104786860729</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>0.9141425530617884</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.08987815961461898</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.4120599366048215</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.416222139537751</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.5431011019718975</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>-0.8508302248275315</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>8.949095557881165</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" s="11" t="n">
+        <v>0.4841257534277288</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0.09873843840412477</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0.4136080577492259</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.4345595122344825</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0.583152664060407</v>
+      </c>
+      <c r="H8" s="11" t="n">
+        <v>-0.8148395028603723</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>11.3495492130162</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>0.2644612436584381</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0.02375507750185046</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0.3285681149493113</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.2367262031189514</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>0.2806795140856809</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>-0.8749236366128393</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>0.8714506981228347</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>2.986136932736587</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>0.0906132753518234</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>0.362881437377765</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.4221323387171251</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0.5189736308577927</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>-0.8396414812946937</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>9.129792235103587</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>0.9732875292324366</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>0.07514726813743411</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0.383062969583496</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0.3820729488129694</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0.4812987284920595</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>-0.7989064118869299</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>5.918621888474384</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>1.155503579239567</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v/>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>0.0584750624215673</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>0.3046931693429364</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>0.3385487158378774</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0.4748947185677542</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>-0.6788079582129238</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>3.559672597467387</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>0.03361307782262157</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0.289283888335773</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0.258406345105917</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0.3588992003222063</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>-0.7924389838970872</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>1.417011496667616</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>0.7585499518433978</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>0.06704552730367386</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>0.2984070864036199</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>0.3660472367355085</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>0.5223509175050569</v>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>-0.6071516370474518</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>4.653640453449366</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="11" t="n">
+        <v>-0.1618290350977913</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0.06466956412794223</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0.2994702043303814</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>0.3583750950650276</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0.5100121262806055</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>-0.6146711513244307</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>4.327028346656062</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>-0.1108846511372912</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0.05471620026182822</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0.301532652712724</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0.3271189803494122</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>0.4571455024941573</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>-0.7001259030666498</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>3.145648114026413</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>0.1209728570768318</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0.03633515953887279</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0.2564258646167044</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>0.2671284518245004</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>0.3572043943604543</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>-0.7697797218098348</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>1.592806452142319</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>0.9255009597798955</v>
+      </c>
+      <c r="M17" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0.06719395367003167</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0.2709347037476466</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>0.3751893958990684</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0.5173636117121397</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>-0.6036786428646497</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>4.674671141465319</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>0.04049514189701764</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0.07502464095269379</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0.2792798323722112</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0.3980992429200452</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0.567673981276738</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>-0.5284632021083417</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>5.897587831647302</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>-0.2138832132397379</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>0.01402235087081638</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>0.6598708221962798</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>0.3480715960671825</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0.5201120177468026</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>-0.8334874602373472</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0.07459684202008288</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>-0.1123200412694773</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0.5732373697414401</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0.07926922843011082</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>0.1055064882524025</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>-0.8334874602373471</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>-0.4594156418970015</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>0.9520983835391278</v>
+      </c>
+      <c r="M21" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>-0.05725142325768773</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>0.5995582460666489</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0.2013578356974359</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0.2814045700093137</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>-0.8334874602373472</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>-0.2624122787303765</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>0.5634211910734011</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>-0.05280324252933744</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0.6227199703769176</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0.2243209773360098</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0.3133050406441812</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>-0.8334874602373473</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>-0.2442678960517294</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>0.4655188679450274</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>-0.1105874380608919</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>0.6200293263421957</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>0.121178488134242</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>0.1706724415745379</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>-0.8360911185686324</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>-0.4539461463389128</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>0.7987965335463224</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>-0.1225732534494648</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0.4468406898246396</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>-0.07016037279672843</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>-0.08173094841400699</v>
+      </c>
+      <c r="H25" s="11" t="n">
+        <v>-0.7350358151692828</v>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>-0.4908862309736607</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>1.348545058120897</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.03557136623897805</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.5333806823089525</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>0.3299231930949357</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0.424779061626277</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>-0.7576587206310881</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.1977603583195127</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="L26" s="11" t="n">
+        <v>0.2781877463947019</v>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>DUOL</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>-0.1234133603813098</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.5463526612123289</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0.03129350459110046</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0.04055110877404131</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>-0.7988565404433809</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>-0.4933978272893468</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>1.098423683688364</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>0.03370417651503521</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>0.06789490615528326</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>0.5221973283652125</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>0.7982584381984438</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>-0.2392477452272798</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>1.226215045406112</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.03370980958751302</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.06790048151209217</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0.522240288683088</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>0.7983896659541889</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>-0.2392477452272798</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>1.226215045406112</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>0.03370980958751302</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>0.06790048151209217</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>0.522240288683088</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>0.7983896659541889</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>-0.2392477452272798</v>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>1.226215045406112</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0.03370980958751302</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0.06790048151209217</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0.522240288683088</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>0.7983896659541889</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>-0.2392477452272798</v>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>1.226215045406112</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>0.03370980958751302</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>0.06790048151209217</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>0.522240288683088</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>0.7983896659541889</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>-0.2392477452272798</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>1.226215045406112</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0.03343681343503535</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.06767516380785676</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>0.5198498647550877</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>0.7928023929527597</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>-0.2440826956053245</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>1.212066366637341</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>0.006745426963743695</v>
+      </c>
+      <c r="M33" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>0.03409216599056109</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0.06749965351020441</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>0.5304213757019554</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>0.8070989716799091</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>-0.232426088418173</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>1.246177490377855</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="11" t="n">
+        <v>-0.008277032074571311</v>
+      </c>
+      <c r="M34" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>0.03370980958751302</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>0.06790048151209217</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>0.522240288683088</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>0.7983896659541889</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>-0.2392477452272798</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>1.226215045406112</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>0.01960487657989041</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>0.01521116913279099</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>1.284027935849295</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>1.799783266370657</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>-0.05707117672507322</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>0.5979760006955412</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>0.01960813086890423</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0.01521241140635071</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>1.284134147174996</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>1.800079137366279</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>-0.05707117672507322</v>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>0.5979760006955412</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>0.01960813086890423</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>0.01521241140635071</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>1.284134147174996</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>1.800079137366279</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>-0.05707117672507322</v>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>0.5979760006955412</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>0.01960813086890423</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>0.01521241140635071</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>1.284134147174996</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>1.800079137366279</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>-0.05707117672507322</v>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>0.5979760006955412</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>0.01960813086890423</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>0.01521241140635071</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>1.284134147174996</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>1.800079137366279</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>-0.05707117672507322</v>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>0.5979760006955412</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>0.01960813086890423</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0.01521241140635071</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>1.284134147174996</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>1.800079137366279</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>-0.05707117672507322</v>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>0.5979760006955412</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>0.01960813086890423</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>0.01521241140635071</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>1.284134147174996</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>1.800079137366279</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>-0.05707117672507322</v>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>0.5979760006955412</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>0.01960813086890423</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0.01521241140635071</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>1.284134147174996</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>1.800079137366279</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>-0.05707117672507322</v>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>0.5979760006955412</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>0.1491637107584858</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0.1695279537052974</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>0.9053509047751095</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>1.113627117737396</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>-0.3399302268072862</v>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>8.295375640156196</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>0.1492032593021795</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>0.1695488705143411</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>0.9054632830697465</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>1.113902768014063</v>
+      </c>
+      <c r="H45" s="11" t="n">
+        <v>-0.3399302268072862</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>8.295375640156196</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>0.1492032593021795</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>0.1695488705143411</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>0.9054632830697465</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>1.113902768014063</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>-0.3399302268072862</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>8.295375640156196</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>0.1492032593021795</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0.1695488705143411</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>0.9054632830697465</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>1.113902768014063</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>-0.3399302268072862</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>8.295375640156196</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>0.1492032593021795</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>0.1695488705143411</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>0.9054632830697465</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>1.113902768014063</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>-0.3399302268072862</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>8.295375640156196</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>0.1285991559350201</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>0.1471697169194991</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>0.8960892661056504</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>1.098844790427607</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>-0.2771448011146757</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>5.955101395132457</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="L49" s="11" t="n">
+        <v>0.3469762546413566</v>
+      </c>
+      <c r="M49" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>0.1403355589744564</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>0.1580223448829602</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>0.910542035463991</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>1.12136614762773</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>-0.2746363913759123</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>7.209812421105982</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L50" s="11" t="n">
+        <v>0.1544544805069981</v>
+      </c>
+      <c r="M50" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>VOO</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>trailing</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>0.1412395085149012</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>0.1588272107280826</v>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>0.9117224171114825</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>1.127076136702849</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>-0.2746363913759123</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>7.314770272941587</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" s="11" t="n">
+        <v>0.1396998087823249</v>
+      </c>
+      <c r="M51" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>Historical backtest on adjusted prices; re-entry after 21 trading days. Not a recommendation to adopt any stop.</t>
         </is>
       </c>
     </row>
@@ -6226,7 +8737,7 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -6332,10 +8843,10 @@
         </is>
       </c>
       <c r="J4" s="11" t="n">
-        <v/>
+        <v>0.355327691196202</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6375,10 +8886,10 @@
         </is>
       </c>
       <c r="J5" s="11" t="n">
-        <v/>
+        <v>0.09467230880379809</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6418,10 +8929,10 @@
         </is>
       </c>
       <c r="J6" s="11" t="n">
-        <v/>
+        <v>0.25</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6461,10 +8972,10 @@
         </is>
       </c>
       <c r="J7" s="11" t="n">
-        <v/>
+        <v>0.175</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6504,10 +9015,10 @@
         </is>
       </c>
       <c r="J8" s="11" t="n">
-        <v/>
+        <v>0.125</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
@@ -33,9 +33,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -125,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,6 +145,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -525,7 +527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-04 18:50 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-04 18:51 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>
@@ -3326,11 +3328,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3581,6 +3586,687 @@
       </c>
       <c r="B26" s="11" t="n">
         <v>0.2041</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>MC success above real capital @ 2% inflation</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>0.8485</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Bootstrap success above real capital @ 2% inflation</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>0.8679</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>MC success above real capital @ 3% inflation</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>0.7921</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Bootstrap success above real capital @ 3% inflation</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>MC success above real capital @ 4% inflation</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>0.7271</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Bootstrap success above real capital @ 4% inflation</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>0.7483</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>MC success above real capital @ 5% inflation</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>0.6552</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Bootstrap success above real capital @ 5% inflation</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>0.6771</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>MC prob terminal above 100% real capital floor</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>0.8485</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>MC prob terminal above 90% real capital floor</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>0.9179</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>MC prob terminal above 80% real capital floor</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>0.9651999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>MC prob terminal above 70% real capital floor</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>0.9898</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Major Drawdown Recovery Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>trough</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>drawdown</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>recovery</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>days_to_recover</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2000-02-24</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>2000-03-08</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>-0.0521921011703137</v>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>2000-03-22</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2000-04-07</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>2000-04-14</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>-0.05466104755209877</v>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>2000-04-27</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2000-05-01</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>2000-05-26</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>-0.05127731982185779</v>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>2000-06-05</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2000-10-03</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>2000-10-18</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>-0.05563111409934318</v>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>2000-11-03</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2000-11-06</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>2002-08-05</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>-0.2738278820192828</v>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>2004-04-08</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>2005-04-07</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>2005-08-10</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>-0.06324292035717383</v>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>2005-11-17</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>2006-04-27</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>2006-07-27</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>-0.07428113354669819</v>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>2006-09-15</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>2007-10-24</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>2008-03-17</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>-0.08861883761513201</v>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>2008-08-08</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>2008-08-11</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>2009-03-02</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>-0.2234914167744868</v>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>2009-10-19</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>2010-04-26</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>2010-07-06</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>-0.0727702413546627</v>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>2010-11-04</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>2011-05-12</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>2011-10-03</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>-0.151462881549703</v>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>2012-02-07</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>2012-04-02</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>2012-06-01</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>-0.05134607162890448</v>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>2012-08-07</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>2014-09-05</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>2014-10-14</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>-0.05901319257984405</v>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>2014-11-05</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>2015-08-25</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>-0.07105828209581821</v>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>2015-10-16</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>2015-12-16</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>-0.09453428136673914</v>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>2016-04-18</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>2018-01-26</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>2018-02-08</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>-0.05294273580221653</v>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>2018-02-26</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>2018-10-01</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>2018-12-24</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>-0.1149527575798448</v>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>2020-02-19</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>2020-03-20</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>-0.1676653273065402</v>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>2020-06-05</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>2020-09-02</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>2020-10-30</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>-0.06650427186097196</v>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>2020-12-02</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>-0.3102036234978799</v>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>-0.07557404153182967</v>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>-0.1835251727933562</v>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>-0.2729570297725958</v>
+      </c>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="10" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -4729,308 +5415,308 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>ADBE,DIS,DUOL,VOO</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Missing sector</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Sector will be assigned via classification lookup.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Growth/Consumer-Tech</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>CORRELATED-GROUP OVERWEIGHT</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>Group 'Growth/Consumer-Tech' totals 45.0% &gt; cap 30%.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>ADBE</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:50:25.797519+00:00'}</t>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:51:43.507137+00:00'}</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:50:25.800034+00:00'}</t>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:51:43.509362+00:00'}</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>DUOL</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>{'status': 'ok', 'inception': '2021-07-28', 'rows': 1302, 'fetched_utc': '2026-10-04T18:50:25.801697+00:00'}</t>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>{'status': 'ok', 'inception': '2021-07-28', 'rows': 1302, 'fetched_utc': '2026-10-04T18:51:43.511320+00:00'}</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>IEF</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:50:25.803463+00:00'}</t>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:51:43.513118+00:00'}</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>SHY</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:50:25.805187+00:00'}</t>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:51:43.515281+00:00'}</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>VOO</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>{'status': 'ok', 'inception': '2010-09-09', 'rows': 4041, 'fetched_utc': '2026-10-04T18:50:25.806728+00:00'}</t>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>{'status': 'ok', 'inception': '2010-09-09', 'rows': 4041, 'fetched_utc': '2026-10-04T18:51:43.517393+00:00'}</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:50:25.808489+00:00'}</t>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:51:43.519527+00:00'}</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>AGG</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>{'status': 'ok', 'inception': '2003-09-29', 'rows': 5790, 'fetched_utc': '2026-10-04T18:50:25.810154+00:00'}</t>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>{'status': 'ok', 'inception': '2003-09-29', 'rows': 5790, 'fetched_utc': '2026-10-04T18:51:43.521581+00:00'}</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Survivorship bias</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Historical analysis is subject to survivorship bias because securities that no longer exist are not represented.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Returns basis</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Adjusted close (dividend/total-return) prices used; returns include dividends.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>P&amp;L</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Dollar P&amp;L is not computed because no cost basis / purchase price was supplied in the input spreadsheet. Return-based attribution is used instead (spec section 64: do not invent data).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Taxes</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Tax effects are excluded because sufficient tax-lot information was not supplied.</t>
         </is>

--- a/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-04 18:51 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-04 19:22 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:51:43.507137+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T19:22:06.849981+00:00'}</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:51:43.509362+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T19:22:06.852541+00:00'}</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2021-07-28', 'rows': 1302, 'fetched_utc': '2026-10-04T18:51:43.511320+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2021-07-28', 'rows': 1302, 'fetched_utc': '2026-10-04T19:22:06.854829+00:00'}</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:51:43.513118+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T19:22:06.857470+00:00'}</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T18:51:43.515281+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2002-07-30', 'rows': 6084, 'fetched_utc': '2026-10-04T19:22:06.861466+00:00'}</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2010-09-09', 'rows': 4041, 'fetched_utc': '2026-10-04T18:51:43.517393+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2010-09-09', 'rows': 4041, 'fetched_utc': '2026-10-04T19:22:06.863315+00:00'}</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T18:51:43.519527+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2000-01-03', 'rows': 6728, 'fetched_utc': '2026-10-04T19:22:06.865102+00:00'}</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>{'status': 'ok', 'inception': '2003-09-29', 'rows': 5790, 'fetched_utc': '2026-10-04T18:51:43.521581+00:00'}</t>
+          <t>{'status': 'ok', 'inception': '2003-09-29', 'rows': 5790, 'fetched_utc': '2026-10-04T19:22:06.866804+00:00'}</t>
         </is>
       </c>
     </row>

--- a/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
@@ -538,7 +538,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-11 21:06 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-11 21:18 UTC | Seed: 42 | Simulations: 10000 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>

--- a/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
@@ -5906,18 +5906,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
     <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5951,25 +5952,30 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>metric_definition</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>current_value</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
@@ -5996,23 +6002,28 @@
           <t>Correlated group 'Growth/Consumer-Tech' total weight</t>
         </is>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>The size of the single bet that several correlated holdings actually represent.</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="n">
         <v>0.4500000000000001</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="G4" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>Correlated-group exposure &gt; configured cap (30.0%)</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Trim the 'Growth/Consumer-Tech' group (ADBE, DIS, DUOL) toward 30.0%; these holdings move together and diversification is overstated.</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>Group 'Growth/Consumer-Tech' (ADBE, DIS, DUOL) totals 45.0% vs a 30.0% cap.</t>
         </is>
@@ -6039,23 +6050,28 @@
           <t>Monte Carlo vs historical bootstrap disagreement</t>
         </is>
       </c>
-      <c r="E5" s="14" t="n">
-        <v>1</v>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>How much the answer depends on which model you believe.</t>
+        </is>
       </c>
       <c r="F5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>Key metrics differ materially between Gaussian MC and real-history bootstrap (&gt;10pp probability or &gt;25% value)</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Report ranges, not point estimates; make reserve/funding decisions using the conservative bootstrap engine.</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>reserve funded differs by 66.3%.</t>
         </is>
@@ -6082,23 +6098,28 @@
           <t>Probability all 10 reserve payments funded</t>
         </is>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Whether the obligation is actually met on time, every time.</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
         <v>0.18</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="G6" s="14" t="n">
         <v>0.9</v>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>min(MC, bootstrap) P(all reserve payments funded) &lt; 90.0%</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Increase the reserve discount buffer, extend the glide path, or reduce payment size; plan against the conservative engine.</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>MC 84.3% / bootstrap 18.0% vs a 90.0% planning standard.</t>
         </is>
@@ -6125,23 +6146,28 @@
           <t>IEF-SHY correlation</t>
         </is>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Whether two holdings move together, which is what decides if they are really two bets or one.</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n">
         <v>0.7847152400355502</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="G7" s="14" t="n">
         <v>0.7</v>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>|Pairwise monthly correlation| &gt; configured threshold (0.70)</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>Treat IEF and SHY as one risk bet when sizing exposure; avoid adding correlated positions.</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>Correlation 0.78 exceeds 0.70.</t>
         </is>
@@ -6168,23 +6194,28 @@
           <t>Monte Carlo P(&gt;20% growth-phase drawdown)</t>
         </is>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>How painful the ride to 2033 is likely to be.</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n">
         <v>0.2766666666666667</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="G8" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>Simulated probability of a &gt;20% drawdown &gt; 25.0% review trigger</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Portfolio-level review triggered: consider glide-path acceleration, band tightening, or a defensive sleeve.</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Monte Carlo: P(&gt;20% drawdown) = 27.7% (median max drawdown -16.4%).</t>
         </is>
@@ -6211,23 +6242,28 @@
           <t>Information Technology sector weight</t>
         </is>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>How much of the plan may sit in one sector.</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n">
         <v>0.355327691196202</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="G9" s="14" t="n">
         <v>0.35</v>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>Sector allocation &gt; configured maximum sector weight (35.0%)</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Review/rebalance Information Technology exposure toward the 35.0% cap.</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>Information Technology: 35.5% of portfolio (ADBE, DUOL).</t>
         </is>
@@ -7439,7 +7475,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-11 23:19 UTC | Seed: 42 | Simulations: 1500 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-11 23:28 UTC | Seed: 42 | Simulations: 1500 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -13076,28 +13112,280 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n"/>
-      <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>max_position_weight</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Position weight cap</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>risk.max_position_weight in the config, compared against each holding's weight.</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>The largest single-name exposure the plan is allowed to carry.</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>A breach says one company, not one sector, can move the whole plan. The severity follows how far past the cap it sits.</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Trim toward the cap in stages rather than in one trade, so the exit does not become the risk.</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>Passing the cap test says nothing about correlated groups: several legal positions can be one economic bet.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>max_sector_weight</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Sector weight cap</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>risk.max_sector_weight in the config, compared against each sector total.</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>How much of the plan may sit in one sector.</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Sector caps catch concentration that position caps miss, because it aggregates several compliant holdings.</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>Reduce the sector total, not just the biggest name in it.</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Sector labels come from a lookup table; an unmapped ticker lands in a catch-all sector and can hide real concentration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>max_correlated_group_weight</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Correlated group cap</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>risk.max_correlated_group_weight in the config, compared against the total weight of holdings whose correlation exceeds risk.correlation_threshold.</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>The size of the single bet that several correlated holdings actually represent.</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>This is the cap that tells the truth about diversification. A portfolio can pass every position and sector cap and still breach this one.</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Trim the group as a unit toward the cap.</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Correlation is estimated on shared history, so a cluster can be understated when a holding has a short record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>min_cash_weight</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Cash floor</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>risk.min_cash_weight in the config, compared against the cash-like weight.</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>The minimum buffer the plan keeps outside market exposure.</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Below the floor, the first payment or the first drawdown has to be funded by selling something at whatever price is available.</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Restore the floor from the next contribution rather than by selling into a fall.</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Cash-like means excluded from simulation, so its return is zero in every scenario - it buys safety, not yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>engine_disagreement</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Engine disagreement spread</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Relative difference between the Monte Carlo and historical bootstrap values of the same metric.</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>How much the answer depends on which model you believe.</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>A large spread is a finding, not noise: it means the assumption set, not the holdings, is driving the answer.</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Report ranges rather than point estimates, and decide on the more conservative engine.</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>The engines answer different questions, so some spread is expected. Only a spread in a decision-relevant metric matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>thesis_coverage</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Thesis coverage</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Number of holdings with no stated investment thesis in the input.</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>How much of the portfolio has no written reason for being there.</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>A missing thesis is not a risk estimate, it is a governance gap: it means nobody wrote down why the position should exist.</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>Write the thesis in the input's thesis column, or remove the position.</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>The model cannot judge whether a thesis is good, only whether one is recorded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n"/>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="n"/>
+      <c r="H80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>Narrative version with the ten most common misreadings: docs/METRIC_DEFINITIONS.md (generated from the same source file).</t>
         </is>
       </c>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
+++ b/portfolio_model/outputs/spreadsheet/portfolio_analysis.xlsx
@@ -28,6 +28,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stop-Loss Backtests" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked Examples" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -940,104 +941,116 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="n"/>
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Worked Examples</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>The arithmetic behind each headline metric, recalculated with this portfolio's own numbers.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Severity legend (used by Rule Flags and Data Quality)</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n"/>
       <c r="B41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>what_it_means</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>The plan fails under the configured rules. Address before relying on any other number.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>A rule is breached in a way that changes the answer. Act on it.</t>
+          <t>The plan fails under the configured rules. Address before relying on any other number.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Outside the configured comfort zone. Review and decide.</t>
+          <t>A rule is breached in a way that changes the answer. Act on it.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>WARNING</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Inside the rules but worth watching over time.</t>
+          <t>Outside the configured comfort zone. Review and decide.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Inside the rules but worth watching over time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Context, not a problem.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="n"/>
-      <c r="B48" s="4" t="n"/>
-    </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>Every metric is defined on the Definitions sheet. The same text generates docs/METRIC_DEFINITIONS.md and the web UI Definitions tab.</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7475,7 +7488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-11 23:28 UTC | Seed: 42 | Simulations: 1500 | Model version: 1.0.0</t>
+          <t>Generated: 2026-10-12 00:17 UTC | Seed: 42 | Simulations: 1500 | Model version: 1.0.0</t>
         </is>
       </c>
     </row>
@@ -13386,6 +13399,956 @@
       <c r="F81" s="4" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Worked examples - the arithmetic behind each headline metric, using your own numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>your_numbers</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>what_it_means</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>the_trap</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>what_to_do</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>weights_source</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Weights source</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Which input column was used: explicit portfolio weights, market value / total, or quantity x price.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>7 holdings: ADBE 22.0%, CASH 12.5%, DIS 9.5%, DUOL 13.5%, IEF 4.3%, SHY 13.2%, VOO 25.0%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>supplied</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>These weights are what every simulation starts from. Total invested contributions are $450,000, and the plan's obligation is $441,127.</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Weights are renormalised to 100%. If your weights summed to 92%, everything is scaled up by 8.7% silently.</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>If the source is not what you intended, fix the spreadsheet column rather than the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>hhi</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>HHI (concentration index)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Sum of squared weights. Normalised version: (HHI - 1/n) / (1 - 1/n).</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>0.220² + 0.125² + 0.095² + 0.135² + 0.043² + 0.132² + 0.250² = 0.1731</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>0.1731</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>With 7 holdings, a perfectly even portfolio would give 0.1429. Yours is 0.1731, so the concentration is real rather than nominal.</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>HHI sees position size only. Two 25% positions in perfectly correlated names look the same as two independent names.</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Use it to argue concentration quantitatively instead of saying 'it feels concentrated'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>effective_n</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Effective number of independent bets</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>1 / HHI, where HHI is the sum of squared weights over all holdings with weight &gt; 0.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>1 / 0.0353 = 5.78</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>You hold 7 positions but they behave like 5.78 independent bets. That is the number the funding probabilities are really built on.</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>It measures weight concentration, not correlation-adjusted independence, so it is an upper bound on real diversification.</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>The rule engine flags it when effective_n falls below 60% of the holding count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>top3_top5_top10</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Top 3 / 5 / 10 weight</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Sum of the largest three, five and ten weights.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>largest VOO 25.0%; top 3 = 60.5% of the portfolio</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Three positions carry 60.5% of the plan. If any one of them halves, the whole terminal value moves by roughly a third of that weight.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>With fewer than 3 holdings the top-3 figure is simply 100%.</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Compare against max_position_weight and max_sector_weight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>correlation_cluster</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Correlation cluster</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Single-linkage grouping of holdings joined by correlation above the threshold.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>IEF, SHY move together (mean correlation 0.78) and carry 17.5% together</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Those 2 holdings are one bet. Treat their combined weight as a single exposure when you compare it to the 30.0% group cap.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Single-linkage can chain A-B and B-C into one cluster even when A-C correlation is modest.</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Apply the correlated-group cap to the cluster, not to each member.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>required_reserve</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Required reserve (present value)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Payment x [1 - (1+r)^-n] / r x (1+r) for n = last_year - first_year + 1 payments at rate = reserve_discount_rate (annuity-due).</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>$50,000/(1+0.029)^0 + $50,000/(1+0.029)^1 + $50,000/(1+0.029)^2 + $50,000/(1+0.029)^3 + $50,000/(1+0.029)^4 + $50,000/(1+0.029)^5 + $50,000/(1+0.029)^6 + $50,000/(1+0.029)^7 + $50,000/(1+0.029)^8 + $50,000/(1+0.029)^9 … = $441,127</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>$441,127</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>10 payments of $50,000 from 2033 to 2042, discounted at 2.9%, must be standing still in 2033. Everything above that is facility surplus.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>It is a present value, not cash you must hold. A reserve exactly equal to it only works if the reserve keeps earning that rate.</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>If the discount rate is wrong, the obligation is wrong: 2.9% here, so test 2% and 4% before committing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>terminal_percentiles</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Terminal percentiles (p5 ... p95)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Percentiles of the simulated 2033 value distribution.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>1,500 simulated outcomes of the 2033 value: p5=$421,535, p25=$557,947, p50=$674,244, p75=$834,769, p95=$1,127,619</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>$674,244</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>The median is $674,244, but half the runs land below it. Against contributions of $450,000, the 5th percentile is $421,535 - that is the number the reserve decision should be sized from.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Percentiles from 10,000 simulations are stable to roughly +/-0.5pp in probability terms, not to the dollar.</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Fund obligations from p5-p10, plan spending from p50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>prob_terminal_gt_start</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Success: terminal &gt; contributions</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Share of simulations where 2033 value &gt; total contributions (nominal).</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>1386 of 1,500 Monte Carlo paths end above $450,000</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>92.4%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Nominal success looks comfortable at 92.4%. Compare it with the bootstrap figure of 95.3%, which only uses sequences that actually happened.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Growing money in nominal terms while losing purchasing power still counts as success here.</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Always read it next to prob_terminal_gt_real_start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>prob_all_payments_funded</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Probability all reserve payments funded</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Share of simulations where the reserve balance never goes below zero at any of the 10 payment dates.</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Monte Carlo: 1265 of 1,500 paths fund all 10 payments; bootstrap: 270 of 1,500</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>84.3% / 18.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>This is the decision metric, and the two engines disagree: 84.3% against 18.0%. Plan against the lower one.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>It requires the reserve to be intact at each payment date; a simulation that ends solvent but was empty in 2037 still fails.</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Below the 90% rule threshold the engine raises a HIGH funding flag: extend the glide path, raise the buffer, or shrink payments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>cvar</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>CVaR / expected shortfall</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Negative of the mean of returns at or beyond the VaR quantile.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>average of the worst 5% of bootstrap outcomes = 7.5% of invested capital</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>In the bad tail the average outcome is a loss of 7.5%</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Terminal CVaR is measured on the 2033 outcome relative to contributions over six years, not on a month. It is a horizon loss, not a monthly one. A NEGATIVE CVaR is not an error: it means that even the worst 5% of simulated outcomes are, on average, still gains - the tail is not loss-making under these assumptions.</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>The rule engine raises a HIGH tail flag above 30% terminal CVaR95.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>max_drawdown_growth</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Max drawdown (growth phase)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Deepest peak-to-trough fall in each simulated path before the 2033 split; reported as a median and as probabilities of exceeding 10/20/30/40%.</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>across the simulations the median worst peak-to-trough is -16.4% and the worst 5% of paths reach -28.6%</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>-28.6%</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>In the unlucky 5% of paths the portfolio falls 28.6% from its peak before the glide end, against a configured review trigger of 20%.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Measured on the growth phase only. Reserve-phase drawdowns are deliberately excluded because that money is already earmarked.</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Above the 25% review trigger the engine raises a drawdown flag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>glide_path</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Glide path targets</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Year-by-year equity/bond/cash targets from glide_path.method between start_equity and end_equity.</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2027: equity 70.0% → 2033: equity 55.0%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Equity moves from 70.0% to 55.0% across the plan - this schedule de-risks only if the end target is below the start weight. The simulations follow it mechanically, so changing the 2033 equity target changes every funding probability.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Glide path changes risk, not expected return much. Its value shows up in drawdown and reserve-funding probabilities, not in the median.</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>Compare the glide variants table: it re-runs the simulation with no glide path, linear, accelerating and custom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>rebalance_band</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Rebalancing band</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Absolute: target +/- band percentage points. Relative: target x (1 +/- relative_band).</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0 of 3 classes sit outside the ±5.0% band</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>With a 5.0% band and 0.1% transaction cost, 0 classes are currently outside the band.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Bands are tested on asset *class* weights at month end, not on individual holdings.</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Check mean_turnover and mean_rebalances to see what the band actually costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>engine_disagreement</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Engine disagreement spread</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Relative difference between the Monte Carlo and historical bootstrap values of the same metric.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>reserve funding: Monte Carlo 84.3% vs bootstrap 18.0% = a 66.3% spread</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>66.3%</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>The engines disagree more than any single holding's weight. That is a statement about the assumptions, not about the portfolio.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>The engines answer different questions, so some spread is expected. Only a spread in a decision-relevant metric matters.</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>Report ranges rather than point estimates, and decide on the more conservative engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>data_provenance</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Data provenance (source / as-of)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Per ticker: cache hit, network download, or committed bundled snapshot, with rows, inception date and data-as-of date.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>prices resolved from: cache (8); earliest as-of 2026-10-09</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>cache</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Two runs of the same portfolio disagree most often because of data vintage, not mathematics. This is the vintage this run used.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Offline reproducibility and live freshness are different goals; the report states which one it used.</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Refresh with `python scripts/build_offline_dataset.py` when you need current prices, or run with --offline for a reproducible result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>max_correlated_group_weight</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>GRP-01 — Correlated group 'Growth/Consumer-Tech' total weight</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Correlated-group exposure &gt; configured cap (30.0%)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>measured 0.4500 against threshold 0.3000</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Group 'Growth/Consumer-Tech' (ADBE, DIS, DUOL) totals 45.0% vs a 30.0% cap.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Correlation is estimated on shared history, so a cluster can be understated when a holding has a short record.</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>Trim the 'Growth/Consumer-Tech' group (ADBE, DIS, DUOL) toward 30.0%; these holdings move together and diversification is overstated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>engine_disagreement</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>MODEL-06 — Monte Carlo vs historical bootstrap disagreement</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Key metrics differ materially between Gaussian MC and real-history bootstrap (&gt;10pp probability or &gt;25% value)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>measured 1.0000 against threshold 1.0000</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>reserve funded differs by 66.3%.</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>The engines answer different questions, so some spread is expected. Only a spread in a decision-relevant metric matters.</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Report ranges, not point estimates; make reserve/funding decisions using the conservative bootstrap engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>prob_all_payments_funded</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>RESV-05 — Probability all 10 reserve payments funded</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>min(MC, bootstrap) P(all reserve payments funded) &lt; 90.0%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>measured 0.1800 against threshold 0.9000</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>MC 84.3% / bootstrap 18.0% vs a 90.0% planning standard.</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>It requires the reserve to be intact at each payment date; a simulation that ends solvent but was empty in 2037 still fails.</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>Increase the reserve discount buffer, extend the glide path, or reduce payment size; plan against the conservative engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Deterministic: every line here is recomputed from this run's results. No model and no generated commentary.</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
